--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,27 +869,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134277109</v>
+        <v>134277146</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>56925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>208260</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>830678</v>
+        <v>830743</v>
       </c>
       <c r="R4" t="n">
-        <v>7330771</v>
+        <v>7330923</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,27 +966,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134277146</v>
+        <v>134277109</v>
       </c>
       <c r="B5" t="n">
-        <v>56925</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208260</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>830743</v>
+        <v>830678</v>
       </c>
       <c r="R5" t="n">
-        <v>7330923</v>
+        <v>7330771</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134277119</v>
+        <v>134277114</v>
       </c>
       <c r="B9" t="n">
-        <v>80337</v>
+        <v>80368</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>830625</v>
+        <v>830516</v>
       </c>
       <c r="R9" t="n">
-        <v>7330784</v>
+        <v>7330938</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134277114</v>
+        <v>134277113</v>
       </c>
       <c r="B10" t="n">
-        <v>80368</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>830516</v>
+        <v>830741</v>
       </c>
       <c r="R10" t="n">
-        <v>7330938</v>
+        <v>7330710</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134277113</v>
+        <v>134277112</v>
       </c>
       <c r="B11" t="n">
         <v>57972</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>830741</v>
+        <v>830733</v>
       </c>
       <c r="R11" t="n">
-        <v>7330710</v>
+        <v>7330703</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134277112</v>
+        <v>134277107</v>
       </c>
       <c r="B12" t="n">
         <v>57972</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>830733</v>
+        <v>830738</v>
       </c>
       <c r="R12" t="n">
-        <v>7330703</v>
+        <v>7330702</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134277107</v>
+        <v>134277115</v>
       </c>
       <c r="B13" t="n">
-        <v>57972</v>
+        <v>80368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>830738</v>
+        <v>830560</v>
       </c>
       <c r="R13" t="n">
-        <v>7330702</v>
+        <v>7330917</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134277115</v>
+        <v>134277125</v>
       </c>
       <c r="B15" t="n">
-        <v>80368</v>
+        <v>79383</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6434</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>830560</v>
+        <v>830529</v>
       </c>
       <c r="R15" t="n">
-        <v>7330917</v>
+        <v>7330930</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134277125</v>
+        <v>134277098</v>
       </c>
       <c r="B16" t="n">
-        <v>79383</v>
+        <v>106295</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>830529</v>
+        <v>830660</v>
       </c>
       <c r="R16" t="n">
-        <v>7330930</v>
+        <v>7330793</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2130,45 +2130,57 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134277098</v>
+        <v>134277143</v>
       </c>
       <c r="B17" t="n">
-        <v>106295</v>
+        <v>99181</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>830660</v>
+        <v>830742</v>
       </c>
       <c r="R17" t="n">
-        <v>7330793</v>
+        <v>7330726</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2209,6 +2221,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2224,6 +2237,1711 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134277141</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99181</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>830590</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7330831</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>7 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134277134</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99181</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>830688</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7330706</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>54 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134277144</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99181</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>830744</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7330686</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134277136</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99181</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>830574</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7330897</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>27 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134277127</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99216</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>830717</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7330743</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134277138</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99181</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>830684</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7330767</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>11 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134277119</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80330</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>388</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stiftgelélav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Collema furfuraceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>830625</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7330784</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134277123</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57165</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>dödad av predator</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>830760</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7330714</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rester av död höna. Antagligen rovfågeldödad.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134277137</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99181</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>830603</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7330804</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>14 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134277106</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>830758</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7330705</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hackspår i basen  på gammal asp</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134277126</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99216</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>830500</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7330955</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134277142</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99181</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>830687</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7330727</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>5 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134277140</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99181</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>830695</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7330707</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>8 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134277139</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99181</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>830761</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7330719</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>9 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134277135</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99181</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>830518</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7330946</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>39 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134277101</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>830733</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7331092</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>uppflygande tupp</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>134277128</v>
       </c>
       <c r="B3" t="n">
-        <v>99216</v>
+        <v>99223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,27 +869,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134277146</v>
+        <v>134277109</v>
       </c>
       <c r="B4" t="n">
-        <v>56925</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208260</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>830743</v>
+        <v>830678</v>
       </c>
       <c r="R4" t="n">
-        <v>7330923</v>
+        <v>7330771</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,27 +966,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134277109</v>
+        <v>134277146</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>56925</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>208260</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>830678</v>
+        <v>830743</v>
       </c>
       <c r="R5" t="n">
-        <v>7330771</v>
+        <v>7330923</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134277147</v>
+        <v>134277116</v>
       </c>
       <c r="B7" t="n">
-        <v>80330</v>
+        <v>80375</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>388</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>830712</v>
+        <v>830572</v>
       </c>
       <c r="R7" t="n">
-        <v>7330754</v>
+        <v>7330908</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134277116</v>
+        <v>134277147</v>
       </c>
       <c r="B8" t="n">
-        <v>80368</v>
+        <v>80337</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>388</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>830572</v>
+        <v>830712</v>
       </c>
       <c r="R8" t="n">
-        <v>7330908</v>
+        <v>7330754</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1357,7 +1357,7 @@
         <v>134277114</v>
       </c>
       <c r="B9" t="n">
-        <v>80368</v>
+        <v>80375</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134277115</v>
+        <v>134277110</v>
       </c>
       <c r="B13" t="n">
-        <v>80368</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>830560</v>
+        <v>830721</v>
       </c>
       <c r="R13" t="n">
-        <v>7330917</v>
+        <v>7330714</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134277110</v>
+        <v>134277115</v>
       </c>
       <c r="B14" t="n">
-        <v>57972</v>
+        <v>80375</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>830721</v>
+        <v>830560</v>
       </c>
       <c r="R14" t="n">
-        <v>7330714</v>
+        <v>7330917</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134277125</v>
+        <v>134277098</v>
       </c>
       <c r="B15" t="n">
-        <v>79383</v>
+        <v>106302</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6434</v>
+        <v>221725</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>830529</v>
+        <v>830660</v>
       </c>
       <c r="R15" t="n">
-        <v>7330930</v>
+        <v>7330793</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134277098</v>
+        <v>134277125</v>
       </c>
       <c r="B16" t="n">
-        <v>106295</v>
+        <v>79390</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>6434</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>830660</v>
+        <v>830529</v>
       </c>
       <c r="R16" t="n">
-        <v>7330793</v>
+        <v>7330930</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2133,7 +2133,7 @@
         <v>134277143</v>
       </c>
       <c r="B17" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>134277141</v>
       </c>
       <c r="B18" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>134277134</v>
       </c>
       <c r="B19" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>134277144</v>
       </c>
       <c r="B20" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>134277136</v>
       </c>
       <c r="B21" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>134277127</v>
       </c>
       <c r="B22" t="n">
-        <v>99216</v>
+        <v>99223</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>134277138</v>
       </c>
       <c r="B23" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>134277119</v>
       </c>
       <c r="B24" t="n">
-        <v>80330</v>
+        <v>80337</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>134277137</v>
       </c>
       <c r="B26" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3309,37 +3309,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134277126</v>
+        <v>134277140</v>
       </c>
       <c r="B28" t="n">
-        <v>99216</v>
+        <v>99188</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>830500</v>
+        <v>830695</v>
       </c>
       <c r="R28" t="n">
-        <v>7330955</v>
+        <v>7330707</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3384,6 +3384,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>8 bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3414,7 +3419,7 @@
         <v>134277142</v>
       </c>
       <c r="B29" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3518,37 +3523,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134277140</v>
+        <v>134277126</v>
       </c>
       <c r="B30" t="n">
-        <v>99181</v>
+        <v>99223</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3557,10 +3562,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>830695</v>
+        <v>830500</v>
       </c>
       <c r="R30" t="n">
-        <v>7330707</v>
+        <v>7330955</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3593,11 +3598,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>8 bladrosetter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3628,7 +3628,7 @@
         <v>134277139</v>
       </c>
       <c r="B31" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>134277135</v>
       </c>
       <c r="B32" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134277108</v>
+        <v>134277119</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>80344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>830775</v>
+        <v>830625</v>
       </c>
       <c r="R2" t="n">
-        <v>7330745</v>
+        <v>7330784</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134277128</v>
+        <v>134277147</v>
       </c>
       <c r="B3" t="n">
-        <v>99223</v>
+        <v>80344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>388</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>830702</v>
+        <v>830712</v>
       </c>
       <c r="R3" t="n">
-        <v>7330767</v>
+        <v>7330754</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +873,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134277109</v>
+        <v>134277130</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>96410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>830678</v>
+        <v>830724</v>
       </c>
       <c r="R4" t="n">
-        <v>7330771</v>
+        <v>7330706</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134277146</v>
+        <v>134277131</v>
       </c>
       <c r="B5" t="n">
-        <v>56925</v>
+        <v>96410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208260</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>830743</v>
+        <v>830453</v>
       </c>
       <c r="R5" t="n">
-        <v>7330923</v>
+        <v>7330963</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134277145</v>
+        <v>134277132</v>
       </c>
       <c r="B6" t="n">
-        <v>57153</v>
+        <v>96410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>830445</v>
+        <v>830455</v>
       </c>
       <c r="R6" t="n">
-        <v>7331010</v>
+        <v>7330979</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134277116</v>
+        <v>134277133</v>
       </c>
       <c r="B7" t="n">
-        <v>80375</v>
+        <v>96410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1175,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>2812</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>830572</v>
+        <v>830722</v>
       </c>
       <c r="R7" t="n">
-        <v>7330908</v>
+        <v>7330716</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1257,32 +1261,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134277147</v>
+        <v>134277125</v>
       </c>
       <c r="B8" t="n">
-        <v>80337</v>
+        <v>79397</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>388</v>
+        <v>6434</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>830712</v>
+        <v>830529</v>
       </c>
       <c r="R8" t="n">
-        <v>7330754</v>
+        <v>7330930</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1357,7 +1361,7 @@
         <v>134277114</v>
       </c>
       <c r="B9" t="n">
-        <v>80375</v>
+        <v>80382</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,32 +1455,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134277113</v>
+        <v>134277115</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>80382</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>830741</v>
+        <v>830560</v>
       </c>
       <c r="R10" t="n">
-        <v>7330710</v>
+        <v>7330917</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,32 +1552,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134277112</v>
+        <v>134277116</v>
       </c>
       <c r="B11" t="n">
-        <v>57972</v>
+        <v>80382</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>830733</v>
+        <v>830572</v>
       </c>
       <c r="R11" t="n">
-        <v>7330703</v>
+        <v>7330908</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1645,14 +1649,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134277107</v>
+        <v>134277105</v>
       </c>
       <c r="B12" t="n">
         <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1680,10 +1684,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>830738</v>
+        <v>830776</v>
       </c>
       <c r="R12" t="n">
-        <v>7330702</v>
+        <v>7330724</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1716,6 +1720,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackspår  på asp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1742,14 +1751,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134277110</v>
+        <v>134277106</v>
       </c>
       <c r="B13" t="n">
         <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1777,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>830721</v>
+        <v>830758</v>
       </c>
       <c r="R13" t="n">
-        <v>7330714</v>
+        <v>7330705</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1813,6 +1822,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackspår i basen  på gammal asp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1839,10 +1853,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134277115</v>
+        <v>134277107</v>
       </c>
       <c r="B14" t="n">
-        <v>80375</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1864,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1888,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>830560</v>
+        <v>830738</v>
       </c>
       <c r="R14" t="n">
-        <v>7330917</v>
+        <v>7330702</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1936,10 +1950,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134277098</v>
+        <v>134277108</v>
       </c>
       <c r="B15" t="n">
-        <v>106302</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1961,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1985,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>830660</v>
+        <v>830775</v>
       </c>
       <c r="R15" t="n">
-        <v>7330793</v>
+        <v>7330745</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2033,10 +2047,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134277125</v>
+        <v>134277109</v>
       </c>
       <c r="B16" t="n">
-        <v>79390</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2058,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2082,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>830529</v>
+        <v>830678</v>
       </c>
       <c r="R16" t="n">
-        <v>7330930</v>
+        <v>7330771</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2130,57 +2144,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134277143</v>
+        <v>134277110</v>
       </c>
       <c r="B17" t="n">
-        <v>99188</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>830742</v>
+        <v>830721</v>
       </c>
       <c r="R17" t="n">
-        <v>7330726</v>
+        <v>7330714</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2221,7 +2223,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2240,53 +2241,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134277141</v>
+        <v>134277112</v>
       </c>
       <c r="B18" t="n">
-        <v>99188</v>
+        <v>57972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>830590</v>
+        <v>830733</v>
       </c>
       <c r="R18" t="n">
-        <v>7330831</v>
+        <v>7330703</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2321,18 +2314,12 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>7 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2351,49 +2338,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134277134</v>
+        <v>134277113</v>
       </c>
       <c r="B19" t="n">
-        <v>99188</v>
+        <v>57972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>830688</v>
+        <v>830741</v>
       </c>
       <c r="R19" t="n">
-        <v>7330706</v>
+        <v>7330710</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2428,18 +2411,12 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>54 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2458,37 +2435,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134277144</v>
+        <v>134277101</v>
       </c>
       <c r="B20" t="n">
-        <v>99188</v>
+        <v>57162</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2497,10 +2474,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>830744</v>
+        <v>830733</v>
       </c>
       <c r="R20" t="n">
-        <v>7330686</v>
+        <v>7331092</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2537,7 +2514,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2 bladrosetter</t>
+          <t>uppflygande tupp</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2546,7 +2523,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2565,49 +2541,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134277136</v>
+        <v>134277145</v>
       </c>
       <c r="B21" t="n">
-        <v>99188</v>
+        <v>57153</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>830574</v>
+        <v>830445</v>
       </c>
       <c r="R21" t="n">
-        <v>7330897</v>
+        <v>7331010</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2642,18 +2614,12 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>27 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2672,10 +2638,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134277127</v>
+        <v>134277123</v>
       </c>
       <c r="B22" t="n">
-        <v>99223</v>
+        <v>57165</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2683,34 +2649,54 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>102613</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>dödad av predator</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>830717</v>
+        <v>830760</v>
       </c>
       <c r="R22" t="n">
-        <v>7330743</v>
+        <v>7330714</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2745,13 +2731,17 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rester av död höna. Antagligen rovfågeldödad.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2770,49 +2760,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134277138</v>
+        <v>134277146</v>
       </c>
       <c r="B23" t="n">
-        <v>99188</v>
+        <v>56925</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>208260</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>830684</v>
+        <v>830743</v>
       </c>
       <c r="R23" t="n">
-        <v>7330767</v>
+        <v>7330923</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2847,18 +2833,12 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>11 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2877,48 +2857,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134277119</v>
+        <v>134277126</v>
       </c>
       <c r="B24" t="n">
-        <v>80337</v>
+        <v>99230</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>388</v>
+        <v>219874</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>830625</v>
+        <v>830500</v>
       </c>
       <c r="R24" t="n">
-        <v>7330784</v>
+        <v>7330955</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2978,10 +2959,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134277123</v>
+        <v>134277127</v>
       </c>
       <c r="B25" t="n">
-        <v>57165</v>
+        <v>99230</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2989,54 +2970,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102613</v>
+        <v>219874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>dödad av predator</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>830760</v>
+        <v>830717</v>
       </c>
       <c r="R25" t="n">
-        <v>7330714</v>
+        <v>7330743</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3071,17 +3032,13 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rester av död höna. Antagligen rovfågeldödad.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3100,49 +3057,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134277137</v>
+        <v>134277128</v>
       </c>
       <c r="B26" t="n">
-        <v>99188</v>
+        <v>99230</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>830603</v>
+        <v>830702</v>
       </c>
       <c r="R26" t="n">
-        <v>7330804</v>
+        <v>7330767</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3177,18 +3130,12 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>14 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3207,45 +3154,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134277106</v>
+        <v>134277134</v>
       </c>
       <c r="B27" t="n">
-        <v>57972</v>
+        <v>99195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>830758</v>
+        <v>830688</v>
       </c>
       <c r="R27" t="n">
-        <v>7330705</v>
+        <v>7330706</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3282,7 +3233,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hackspår i basen  på gammal asp</t>
+          <t>54 bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3291,6 +3242,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3309,10 +3261,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134277140</v>
+        <v>134277135</v>
       </c>
       <c r="B28" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3339,7 +3291,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>39</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3348,10 +3300,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>830695</v>
+        <v>830518</v>
       </c>
       <c r="R28" t="n">
-        <v>7330707</v>
+        <v>7330946</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3388,7 +3340,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>8 bladrosetter</t>
+          <t>39 bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3416,10 +3368,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134277142</v>
+        <v>134277136</v>
       </c>
       <c r="B29" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3446,7 +3398,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3455,10 +3407,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>830687</v>
+        <v>830574</v>
       </c>
       <c r="R29" t="n">
-        <v>7330727</v>
+        <v>7330897</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3495,7 +3447,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>5 bladrosetter</t>
+          <t>27 bladrosetter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3523,37 +3475,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134277126</v>
+        <v>134277137</v>
       </c>
       <c r="B30" t="n">
-        <v>99223</v>
+        <v>99195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3562,10 +3514,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>830500</v>
+        <v>830603</v>
       </c>
       <c r="R30" t="n">
-        <v>7330955</v>
+        <v>7330804</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3598,6 +3550,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>14 bladrosetter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3625,10 +3582,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134277139</v>
+        <v>134277138</v>
       </c>
       <c r="B31" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3655,7 +3612,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3664,10 +3621,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>830761</v>
+        <v>830684</v>
       </c>
       <c r="R31" t="n">
-        <v>7330719</v>
+        <v>7330767</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3704,7 +3661,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>9 bladrosetter</t>
+          <t>11 bladrosetter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3732,10 +3689,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134277135</v>
+        <v>134277139</v>
       </c>
       <c r="B32" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3762,7 +3719,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3771,10 +3728,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>830518</v>
+        <v>830761</v>
       </c>
       <c r="R32" t="n">
-        <v>7330946</v>
+        <v>7330719</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3811,7 +3768,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>39 bladrosetter</t>
+          <t>9 bladrosetter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3839,37 +3796,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134277101</v>
+        <v>134277140</v>
       </c>
       <c r="B33" t="n">
-        <v>57162</v>
+        <v>99195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3878,10 +3835,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>830733</v>
+        <v>830695</v>
       </c>
       <c r="R33" t="n">
-        <v>7331092</v>
+        <v>7330707</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3918,7 +3875,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>uppflygande tupp</t>
+          <t>8 bladrosetter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3927,6 +3884,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3942,6 +3900,538 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134277141</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>830590</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7330831</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>7 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134277142</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>830687</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7330727</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>5 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134277143</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>830742</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7330726</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134277144</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>830744</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7330686</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134277098</v>
+      </c>
+      <c r="B38" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>830660</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7330793</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277119</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277147</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277130</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277131</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277132</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277133</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277125</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277114</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277115</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277116</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277105</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1850,6 +1910,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277106</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1947,6 +2012,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277107</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2044,6 +2114,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277108</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2141,6 +2216,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277109</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2238,6 +2318,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277110</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2335,6 +2420,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277112</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2432,6 +2522,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277113</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2538,6 +2633,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277101</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2635,6 +2735,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277145</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2757,6 +2862,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277123</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2854,6 +2964,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277146</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2956,6 +3071,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277126</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3054,6 +3174,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277127</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3151,6 +3276,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277128</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3258,6 +3388,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277134</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3365,6 +3500,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277135</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3472,6 +3612,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277136</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3579,6 +3724,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277137</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3686,6 +3836,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277138</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3793,6 +3948,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277139</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3900,6 +4060,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277140</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4011,6 +4176,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277141</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4118,6 +4288,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277142</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4228,6 +4403,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277143</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4335,6 +4515,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277144</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4432,8 +4617,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277098</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>